--- a/SGC-CKN/Excel/51eee52a-8d55-4898-8a87-84a07d253005_P1-32_P1-32_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/51eee52a-8d55-4898-8a87-84a07d253005_P1-32_P1-32_D800_18-03-2026.xlsx
@@ -35,6 +35,9 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
+    <t>P7-32</t>
+  </si>
+  <si>
     <t>Tên Máy khoan</t>
   </si>
   <si>
@@ -112,11 +115,11 @@
     <t>Sét pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">23:50
+    <t xml:space="preserve">23:30
 17/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">23:59
+    <t xml:space="preserve">23:39
 17/03/2026</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
   <si>
     <t xml:space="preserve">00:17
 18/03/2026</t>
-  </si>
-  <si>
-    <t>Thời gian ghi chép có sự mâu thuẫn giữa lớp 2 (kết thúc 23:59) và lớp 3 (bắt đầu 23:40).</t>
   </si>
   <si>
     <t>11</t>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1145,10 +1145,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1180,57 +1180,57 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>7.67</v>
@@ -1239,30 +1239,30 @@
         <v>0.32</v>
       </c>
       <c r="I11" s="5">
-        <v>4.1</v>
+        <v>7.67</v>
       </c>
       <c r="J11" s="8">
-        <v>12.95</v>
+        <v>24.22</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>7.67</v>
@@ -1280,24 +1280,24 @@
         <v>10.6</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>9.26</v>
@@ -1315,7 +1315,7 @@
         <v>13.3</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1323,7 +1323,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>40</v>
@@ -1350,7 +1350,7 @@
         <v>5.38</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,7 +1358,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>44</v>
@@ -1385,7 +1385,7 @@
         <v>4.14</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1393,7 +1393,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>48</v>
@@ -1420,7 +1420,7 @@
         <v>3.43</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1428,7 +1428,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>51</v>
@@ -1455,7 +1455,7 @@
         <v>2.18</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>54</v>
@@ -1490,7 +1490,7 @@
         <v>0.6</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,7 +1498,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>56</v>
@@ -1525,7 +1525,7 @@
         <v>1.8</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,7 +1533,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>59</v>
@@ -1560,7 +1560,7 @@
         <v>3.18</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
         <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>63</v>
@@ -1703,16 +1703,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>7.67</v>
@@ -1721,10 +1721,10 @@
         <v>0.32</v>
       </c>
       <c r="H2" s="5">
-        <v>4.1</v>
+        <v>7.67</v>
       </c>
       <c r="I2" s="8">
-        <v>12.95</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1732,10 +1732,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>40</v>
@@ -1819,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>44</v>
@@ -1848,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>48</v>
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>51</v>
@@ -1906,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>54</v>
@@ -1935,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>56</v>
@@ -1964,7 +1964,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>59</v>
@@ -1993,16 +1993,16 @@
         <v>70</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="40">
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>44.95</v>
@@ -2011,10 +2011,10 @@
         <v>11.77</v>
       </c>
       <c r="H12" s="40">
-        <v>41.38</v>
+        <v>44.95</v>
       </c>
       <c r="I12" s="40">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/51eee52a-8d55-4898-8a87-84a07d253005_P1-32_P1-32_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/51eee52a-8d55-4898-8a87-84a07d253005_P1-32_P1-32_D800_18-03-2026.xlsx
@@ -35,9 +35,6 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-32</t>
-  </si>
-  <si>
     <t>Tên Máy khoan</t>
   </si>
   <si>
@@ -115,11 +112,11 @@
     <t>Sét pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">23:30
+    <t xml:space="preserve">23:50
 17/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">23:39
+    <t xml:space="preserve">23:59
 17/03/2026</t>
   </si>
   <si>
@@ -135,6 +132,9 @@
   <si>
     <t xml:space="preserve">00:17
 18/03/2026</t>
+  </si>
+  <si>
+    <t>Thời gian ghi chép có sự mâu thuẫn giữa lớp 2 (kết thúc 23:59) và lớp 3 (bắt đầu 23:40).</t>
   </si>
   <si>
     <t>11</t>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1145,10 +1145,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1180,57 +1180,57 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="G11" s="5">
         <v>7.67</v>
@@ -1239,30 +1239,30 @@
         <v>0.32</v>
       </c>
       <c r="I11" s="5">
-        <v>7.67</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="8">
-        <v>24.22</v>
+        <v>12.95</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>7.67</v>
@@ -1280,24 +1280,24 @@
         <v>10.6</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>9.26</v>
@@ -1315,7 +1315,7 @@
         <v>13.3</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1323,7 +1323,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>40</v>
@@ -1350,7 +1350,7 @@
         <v>5.38</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,7 +1358,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>44</v>
@@ -1385,7 +1385,7 @@
         <v>4.14</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1393,7 +1393,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>48</v>
@@ -1420,7 +1420,7 @@
         <v>3.43</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1428,7 +1428,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>51</v>
@@ -1455,7 +1455,7 @@
         <v>2.18</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>54</v>
@@ -1490,7 +1490,7 @@
         <v>0.6</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,7 +1498,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>56</v>
@@ -1525,7 +1525,7 @@
         <v>1.8</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,7 +1533,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>59</v>
@@ -1560,7 +1560,7 @@
         <v>3.18</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
         <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>63</v>
@@ -1703,16 +1703,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="F2" s="5">
         <v>7.67</v>
@@ -1721,10 +1721,10 @@
         <v>0.32</v>
       </c>
       <c r="H2" s="5">
-        <v>7.67</v>
+        <v>4.1</v>
       </c>
       <c r="I2" s="8">
-        <v>24.22</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1732,10 +1732,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>40</v>
@@ -1819,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>44</v>
@@ -1848,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>48</v>
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>51</v>
@@ -1906,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>54</v>
@@ -1935,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>56</v>
@@ -1964,7 +1964,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>59</v>
@@ -1993,16 +1993,16 @@
         <v>70</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="40">
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="F12" s="40">
         <v>44.95</v>
@@ -2011,10 +2011,10 @@
         <v>11.77</v>
       </c>
       <c r="H12" s="40">
-        <v>44.95</v>
+        <v>41.38</v>
       </c>
       <c r="I12" s="40">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/51eee52a-8d55-4898-8a87-84a07d253005_P1-32_P1-32_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/51eee52a-8d55-4898-8a87-84a07d253005_P1-32_P1-32_D800_18-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
+    <t>P7-32</t>
+  </si>
+  <si>
     <t>Tên Máy khoan</t>
   </si>
   <si>
@@ -89,10 +92,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">23:10
@@ -106,17 +109,17 @@
     <t/>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Sét pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:50
+    <t>2</t>
+  </si>
+  <si>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:30
 17/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">23:59
+    <t xml:space="preserve">23:39
 17/03/2026</t>
   </si>
   <si>
@@ -134,13 +137,10 @@
 18/03/2026</t>
   </si>
   <si>
-    <t>Thời gian ghi chép có sự mâu thuẫn giữa lớp 2 (kết thúc 23:59) và lớp 3 (bắt đầu 23:40).</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">00:18
@@ -151,10 +151,10 @@
 18/03/2026</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">01:07
@@ -165,20 +165,20 @@
 18/03/2026</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">05:00
 18/03/2026</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:10
@@ -188,24 +188,21 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:50
 18/03/2026</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">10:10
 18/03/2026</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -1097,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1111,10 +1108,10 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1128,10 +1125,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1145,10 +1142,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1162,10 +1159,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1180,57 +1177,57 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>7.67</v>
@@ -1239,30 +1236,30 @@
         <v>0.32</v>
       </c>
       <c r="I11" s="5">
-        <v>4.1</v>
+        <v>7.67</v>
       </c>
       <c r="J11" s="8">
-        <v>12.95</v>
+        <v>24.22</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>7.67</v>
@@ -1280,24 +1277,24 @@
         <v>10.6</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>9.26</v>
@@ -1315,7 +1312,7 @@
         <v>13.3</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1323,7 +1320,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>40</v>
@@ -1350,7 +1347,7 @@
         <v>5.38</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,7 +1355,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>44</v>
@@ -1385,7 +1382,7 @@
         <v>4.14</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1393,7 +1390,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>48</v>
@@ -1420,7 +1417,7 @@
         <v>3.43</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1428,7 +1425,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>51</v>
@@ -1455,7 +1452,7 @@
         <v>2.18</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,7 +1460,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>54</v>
@@ -1490,24 +1487,24 @@
         <v>0.6</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>55</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" s="32">
         <v>39.9</v>
@@ -1525,24 +1522,24 @@
         <v>1.8</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="36" t="s">
+      <c r="D20" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>59</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>60</v>
       </c>
       <c r="F20" s="35">
         <v>42.3</v>
@@ -1560,12 +1557,12 @@
         <v>3.18</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1671,31 +1668,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,16 +1700,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>7.67</v>
@@ -1721,10 +1718,10 @@
         <v>0.32</v>
       </c>
       <c r="H2" s="5">
-        <v>4.1</v>
+        <v>7.67</v>
       </c>
       <c r="I2" s="8">
-        <v>12.95</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1732,10 +1729,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1761,10 +1758,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1790,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>40</v>
@@ -1819,7 +1816,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>44</v>
@@ -1848,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>48</v>
@@ -1877,7 +1874,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>51</v>
@@ -1906,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>54</v>
@@ -1935,10 +1932,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -1964,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
@@ -1990,19 +1987,19 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="40">
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>44.95</v>
@@ -2011,10 +2008,10 @@
         <v>11.77</v>
       </c>
       <c r="H12" s="40">
-        <v>41.38</v>
+        <v>44.95</v>
       </c>
       <c r="I12" s="40">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
     </row>
   </sheetData>
